--- a/VerveStacks_EGY_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_EGY_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EGY_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25EF9B50-CD02-4E3A-96B3-3F5DDB1997BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48F4C638-13BB-4527-9BC4-A8CC6B0F3635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5B6A77D9-53FA-4062-918A-D1A2A778C9D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6B59CB0A-E2C6-4F7E-A09B-B536C0569C72}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -622,7 +622,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76621C49-88C2-4E7D-AD8E-F17BA5C337F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B47B05-2131-4ED1-95B8-75E0B35273F2}">
   <dimension ref="B3:L25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
